--- a/Dataset_0/4_Integration_results/Stats_table_region.xlsx
+++ b/Dataset_0/4_Integration_results/Stats_table_region.xlsx
@@ -419,19 +419,19 @@
         <v>6</v>
       </c>
       <c r="B2" t="n">
-        <v>52.4</v>
+        <v>61.5</v>
       </c>
       <c r="C2" t="n">
-        <v>52.4</v>
+        <v>61.5</v>
       </c>
       <c r="D2" t="n">
-        <v>52.4</v>
+        <v>61.5</v>
       </c>
       <c r="E2" t="n">
-        <v>52.4</v>
+        <v>61.5</v>
       </c>
       <c r="F2" t="n">
-        <v>52.4</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="3">
@@ -439,19 +439,19 @@
         <v>7</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0582324399822059</v>
+        <v>0.0194161844445864</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0582324399822059</v>
+        <v>0.0194161844445864</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>0.421285668783672</v>
+        <v>0.132775219495663</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0681833468188176</v>
+        <v>0.0170558260679653</v>
       </c>
     </row>
     <row r="4">
@@ -459,17 +459,17 @@
         <v>8</v>
       </c>
       <c r="B4" t="n">
-        <v>49.6</v>
+        <v>57.5</v>
       </c>
       <c r="C4" t="n">
-        <v>49.6</v>
+        <v>57.5</v>
       </c>
       <c r="D4"/>
       <c r="E4" t="n">
-        <v>49.4</v>
+        <v>57.2</v>
       </c>
       <c r="F4" t="n">
-        <v>49.6</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="5">
@@ -477,19 +477,19 @@
         <v>9</v>
       </c>
       <c r="B5" t="n">
-        <v>0.973355332408065</v>
+        <v>0.891458147768309</v>
       </c>
       <c r="C5" t="n">
-        <v>0.973355332408065</v>
+        <v>0.891458147768309</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>0.906639605151107</v>
+        <v>0.76760425486897</v>
       </c>
       <c r="F5" t="n">
-        <v>0.978262265803932</v>
+        <v>0.870191820094649</v>
       </c>
     </row>
     <row r="6">
@@ -497,17 +497,17 @@
         <v>10</v>
       </c>
       <c r="B6" t="n">
-        <v>47.9</v>
+        <v>57.7</v>
       </c>
       <c r="C6" t="n">
-        <v>47.9</v>
+        <v>57.7</v>
       </c>
       <c r="D6"/>
       <c r="E6" t="n">
-        <v>49.2</v>
+        <v>58.7</v>
       </c>
       <c r="F6" t="n">
-        <v>47.9</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="7">
@@ -515,19 +515,19 @@
         <v>11</v>
       </c>
       <c r="B7" t="n">
-        <v>0.973355332408065</v>
+        <v>0.891458147768309</v>
       </c>
       <c r="C7" t="n">
-        <v>0.973355332408065</v>
+        <v>0.891458147768309</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>0.906639605151107</v>
+        <v>0.76760425486897</v>
       </c>
       <c r="F7" t="n">
-        <v>0.978262265803932</v>
+        <v>0.870191820094649</v>
       </c>
     </row>
     <row r="8">
@@ -535,17 +535,17 @@
         <v>12</v>
       </c>
       <c r="B8" t="n">
-        <v>47.2</v>
+        <v>55.5</v>
       </c>
       <c r="C8" t="n">
-        <v>47.2</v>
+        <v>55.5</v>
       </c>
       <c r="D8"/>
       <c r="E8" t="n">
-        <v>49.4</v>
+        <v>57.7</v>
       </c>
       <c r="F8" t="n">
-        <v>47.8</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="9">
@@ -553,19 +553,19 @@
         <v>13</v>
       </c>
       <c r="B9" t="n">
-        <v>0.973355332408065</v>
+        <v>0.901729748846884</v>
       </c>
       <c r="C9" t="n">
-        <v>0.973355332408065</v>
+        <v>0.901729748846884</v>
       </c>
       <c r="D9" t="n">
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>0.906639605151107</v>
+        <v>0.76760425486897</v>
       </c>
       <c r="F9" t="n">
-        <v>0.978262265803932</v>
+        <v>0.926670891546138</v>
       </c>
     </row>
     <row r="10">
@@ -573,17 +573,17 @@
         <v>14</v>
       </c>
       <c r="B10" t="n">
-        <v>43.5</v>
+        <v>56.5</v>
       </c>
       <c r="C10" t="n">
-        <v>43.5</v>
+        <v>56.5</v>
       </c>
       <c r="D10"/>
       <c r="E10" t="n">
-        <v>42.2</v>
+        <v>55.6</v>
       </c>
       <c r="F10" t="n">
-        <v>43.5</v>
+        <v>56.5</v>
       </c>
     </row>
     <row r="11">
@@ -591,19 +591,19 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>0.973355332408065</v>
+        <v>0.891458147768309</v>
       </c>
       <c r="C11" t="n">
-        <v>0.973355332408065</v>
+        <v>0.891458147768309</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>0.906639605151107</v>
+        <v>0.76760425486897</v>
       </c>
       <c r="F11" t="n">
-        <v>0.978262265803932</v>
+        <v>0.870191820094649</v>
       </c>
     </row>
     <row r="12">
@@ -611,17 +611,17 @@
         <v>16</v>
       </c>
       <c r="B12" t="n">
-        <v>52.6</v>
+        <v>56.6</v>
       </c>
       <c r="C12" t="n">
-        <v>52.6</v>
+        <v>56.6</v>
       </c>
       <c r="D12"/>
       <c r="E12" t="n">
-        <v>50.8</v>
+        <v>55.9</v>
       </c>
       <c r="F12" t="n">
-        <v>52.6</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="13">
@@ -629,19 +629,19 @@
         <v>17</v>
       </c>
       <c r="B13" t="n">
-        <v>0.973355332408065</v>
+        <v>0.891458147768309</v>
       </c>
       <c r="C13" t="n">
-        <v>0.973355332408065</v>
+        <v>0.891458147768309</v>
       </c>
       <c r="D13" t="n">
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>0.906639605151107</v>
+        <v>0.76760425486897</v>
       </c>
       <c r="F13" t="n">
-        <v>0.978262265803932</v>
+        <v>0.870191820094649</v>
       </c>
     </row>
   </sheetData>
